--- a/templates/emax/po.xlsx
+++ b/templates/emax/po.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6550"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="EMAX PO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EMAX PO'!$A$19:$G$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'EMAX PO'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'EMAX PO'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>E MAX SPORT PTE. LTD.</t>
   </si>
@@ -45,118 +45,36 @@
     <t>PO Number:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>RO new PO template A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"Purchasing Document"</t>
-    </r>
-  </si>
-  <si>
     <t>ETD (Baseline Date for FOB Term):</t>
   </si>
   <si>
     <t>Incoterm:</t>
   </si>
   <si>
-    <t>FOB USA</t>
-  </si>
-  <si>
-    <t>固定值</t>
-  </si>
-  <si>
     <t>Document Date:</t>
   </si>
   <si>
-    <t>文件创建时间</t>
-  </si>
-  <si>
     <t>Payment Terms:</t>
   </si>
   <si>
-    <t>Net 90 days</t>
-  </si>
-  <si>
     <t>Shipment Ex-factory Date:</t>
   </si>
   <si>
-    <t>手动更新</t>
-  </si>
-  <si>
     <t>Bill To:</t>
   </si>
   <si>
     <t>Ship to:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">根据RO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>PO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（pdf文件）</t>
-    </r>
-  </si>
-  <si>
     <t>Port of Loading:</t>
   </si>
   <si>
-    <t>China</t>
-  </si>
-  <si>
     <t>Supplier Company Name</t>
   </si>
   <si>
-    <t>GLOBALSINO PTE.LTD.</t>
-  </si>
-  <si>
     <t>Final Destination</t>
   </si>
   <si>
-    <t>USA</t>
-  </si>
-  <si>
     <t>Supplier Company Name Address</t>
   </si>
   <si>
@@ -184,185 +102,13 @@
     <t>EX-FACTORY DATE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>RO new PO template I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"Material"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>RO new PO template J</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"Model",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>data base J</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>RO new PO template N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> “Order Quantity”</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Sub-Total </t>
+    <t>Sub-Total</t>
   </si>
   <si>
     <t>Signature:</t>
   </si>
   <si>
-    <t>Tina</t>
-  </si>
-  <si>
     <t>Date:</t>
-  </si>
-  <si>
-    <t>创建时间</t>
   </si>
 </sst>
 </file>
@@ -379,7 +125,7 @@
     <numFmt numFmtId="178" formatCode="mmm/dd/yyyy"/>
     <numFmt numFmtId="179" formatCode="mmm\-dd\-yyyy"/>
     <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="181" formatCode="dd\/mmm\/yy"/>
+    <numFmt numFmtId="181" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="52">
     <font>
@@ -428,7 +174,13 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF00B0F0"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -730,12 +482,6 @@
       <name val="新細明體"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="50">
     <fill>
@@ -1033,7 +779,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1072,26 +818,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1306,319 +1032,319 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="36" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="33" fillId="36" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="39" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="34" fillId="36" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="39" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="41" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="41" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="34" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="34" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="44" fillId="48" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="45" fillId="49" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="46" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="47" fillId="48" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="48" fillId="39" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="50" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="35" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="44" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="45" fillId="48" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="46" fillId="49" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="47" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="48" fillId="48" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="49" fillId="39" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="50" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="51" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="71">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1690,6 +1416,27 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1697,32 +1444,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="5" fillId="2" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="76" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1735,7 +1460,7 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1746,16 +1471,13 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="88" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="2" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1828,36 +1550,21 @@
     <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="76" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="2" borderId="4" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="86" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="98" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="57" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="0" xfId="98" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="40" fontId="5" fillId="2" borderId="4" xfId="98" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="75" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="5" xfId="98" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="75" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="181" fontId="5" fillId="2" borderId="1" xfId="86" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="86" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1865,9 +1572,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="2" xfId="86" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="0" xfId="86" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1993,6 +1697,7 @@
   <colors>
     <mruColors>
       <color rgb="00FFFF99"/>
+      <color rgb="00FF0000"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2292,16 +1997,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6"/>
   <cols>
     <col min="1" max="1" width="17.75" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.25" style="4" customWidth="1"/>
     <col min="3" max="3" width="11" style="4" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="28.375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.75" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="24.9910714285714" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.5803571428571" style="4" customWidth="1"/>
+    <col min="6" max="6" width="27.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.3214285714286" style="4" customWidth="1"/>
     <col min="8" max="8" width="16.5" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.375" style="5" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
@@ -2368,65 +2073,49 @@
       <c r="H5" s="17"/>
       <c r="I5" s="18"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
+    <row r="6" s="2" customFormat="1" ht="51" customHeight="1" spans="1:9">
       <c r="A6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="19"/>
-      <c r="C6" s="20" t="s">
-        <v>4</v>
-      </c>
+      <c r="C6" s="20"/>
       <c r="D6" s="21"/>
       <c r="E6" s="13"/>
       <c r="F6" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="23"/>
       <c r="H6" s="24"/>
       <c r="I6" s="25"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
+    <row r="7" s="2" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>8</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="21"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="28">
-        <v>45910</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>10</v>
-      </c>
+      <c r="F7" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="24"/>
       <c r="I7" s="25"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
+    <row r="8" s="2" customFormat="1" ht="50" customHeight="1" spans="1:9">
       <c r="A8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="21"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="30" t="s">
-        <v>14</v>
-      </c>
+      <c r="F8" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="30"/>
+      <c r="H8" s="24"/>
       <c r="I8" s="25"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
@@ -2442,45 +2131,39 @@
     </row>
     <row r="10" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
       <c r="A10" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B10" s="34"/>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
       <c r="E10" s="36"/>
       <c r="F10" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G10" s="34"/>
       <c r="H10" s="34"/>
-      <c r="I10" s="38" t="s">
-        <v>17</v>
-      </c>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
       <c r="E11" s="36"/>
       <c r="F11" s="16"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
       <c r="I11" s="33"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
       <c r="A12" s="31"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
       <c r="E12" s="36"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
       <c r="I12" s="33"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
@@ -2489,46 +2172,40 @@
       <c r="C13" s="36"/>
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
-      <c r="F13" s="42"/>
+      <c r="F13" s="41"/>
       <c r="G13" s="13"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="44"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
       <c r="A14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="36"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="44"/>
+        <v>12</v>
+      </c>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="18.95" customHeight="1" spans="1:9">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="36"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="46"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="44"/>
+        <v>14</v>
+      </c>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="15.95" customHeight="1" spans="1:9">
       <c r="A16" s="31"/>
@@ -2536,10 +2213,10 @@
       <c r="C16" s="36"/>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="44"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="24" customHeight="1" spans="1:9">
       <c r="A17" s="31"/>
@@ -2547,175 +2224,145 @@
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
-      <c r="I17" s="44"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A18" s="51"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="53"/>
+      <c r="A18" s="50"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:9">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:9">
+      <c r="A20" s="59"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:9">
+      <c r="A21" s="59"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+    </row>
+    <row r="22" ht="15.95" customHeight="1" spans="1:9">
+      <c r="A22" s="51"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="65"/>
+    </row>
+    <row r="23" ht="15.95" customHeight="1" spans="1:9">
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="67"/>
+      <c r="H23" s="68"/>
+    </row>
+    <row r="24" ht="15.95" customHeight="1" spans="1:9">
+      <c r="A24" s="50"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="52"/>
+    </row>
+    <row r="25" ht="15.95" customHeight="1" spans="1:9">
+      <c r="A25" s="10"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="52"/>
+    </row>
+    <row r="26" ht="31" customHeight="1" spans="1:9">
+      <c r="A26" s="10"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="57" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="59" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" ht="70" customHeight="1" spans="1:9">
-      <c r="A20" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:9">
-      <c r="A21" s="60"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="66"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:9">
-      <c r="A22" s="60"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="66"/>
-    </row>
-    <row r="23" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A23" s="52"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="67" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="68"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="70"/>
-    </row>
-    <row r="24" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A24" s="52"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="53"/>
-    </row>
-    <row r="25" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A25" s="51"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="53"/>
-    </row>
-    <row r="26" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A26" s="10"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="H26" s="74"/>
-      <c r="I26" s="53"/>
-    </row>
-    <row r="27" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A27" s="10"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="75" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="77" t="s">
-        <v>42</v>
-      </c>
+      <c r="G26" s="29"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="24"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="50"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="52"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="51"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="53"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="51"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="53"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="5">
